--- a/data/trans_dic/P19C07-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C07-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 8,79</t>
+          <t>3,78; 8,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 12,26</t>
+          <t>6,29; 12,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 8,55</t>
+          <t>3,37; 8,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 12,95</t>
+          <t>3,43; 14,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 9,94</t>
+          <t>4,91; 9,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 12,08</t>
+          <t>6,1; 12,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 10,76</t>
+          <t>5,22; 10,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 13,82</t>
+          <t>4,17; 12,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,25</t>
+          <t>4,95; 8,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 11,15</t>
+          <t>6,96; 11,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,42</t>
+          <t>4,94; 8,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 10,91</t>
+          <t>4,6; 11,27</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,95</t>
+          <t>2,49; 5,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 6,58</t>
+          <t>3,05; 6,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,59</t>
+          <t>2,27; 5,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 8,57</t>
+          <t>2,91; 8,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,04</t>
+          <t>2,46; 6,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 8,11</t>
+          <t>3,89; 8,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,06</t>
+          <t>3,81; 7,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,35</t>
+          <t>4,23; 10,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,31</t>
+          <t>2,86; 5,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,64</t>
+          <t>3,73; 6,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,02</t>
+          <t>3,32; 6,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 8,46</t>
+          <t>4,28; 8,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,57</t>
+          <t>1,12; 3,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,26</t>
+          <t>1,47; 4,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,33</t>
+          <t>2,02; 5,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,6</t>
+          <t>2,07; 5,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,31</t>
+          <t>1,67; 4,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,84</t>
+          <t>2,09; 4,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,22</t>
+          <t>1,43; 4,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,85</t>
+          <t>2,95; 5,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,52</t>
+          <t>1,71; 3,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,08</t>
+          <t>2,11; 4,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,98</t>
+          <t>2,05; 4,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,04</t>
+          <t>2,9; 5,01</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,11</t>
+          <t>2,1; 6,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,82</t>
+          <t>0,86; 3,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,23</t>
+          <t>0,77; 3,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,63</t>
+          <t>0,92; 3,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,97</t>
+          <t>1,18; 3,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,74</t>
+          <t>1,14; 3,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,05</t>
+          <t>1,71; 4,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,63</t>
+          <t>2,2; 4,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,21</t>
+          <t>1,91; 4,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,28</t>
+          <t>1,28; 3,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,47</t>
+          <t>1,55; 3,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,7</t>
+          <t>1,55; 3,6</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,3</t>
+          <t>0,35; 3,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,05</t>
+          <t>0,29; 3,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,69</t>
+          <t>0,57; 3,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,5</t>
+          <t>0,63; 2,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,58</t>
+          <t>0,71; 4,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,86</t>
+          <t>0,5; 2,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,11</t>
+          <t>0,81; 3,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,09</t>
+          <t>1,86; 3,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,98</t>
+          <t>0,86; 3,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,48</t>
+          <t>0,56; 2,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,02</t>
+          <t>0,98; 2,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,81</t>
+          <t>1,41; 2,77</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,73</t>
+          <t>2,48; 8,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,96</t>
+          <t>0,39; 4,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,54</t>
+          <t>1,34; 4,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,1</t>
+          <t>1,52; 5,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,08</t>
+          <t>0,63; 4,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,42</t>
+          <t>0,78; 5,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,93</t>
+          <t>0,49; 2,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,71</t>
+          <t>2,27; 5,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,85</t>
+          <t>0,52; 2,79</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,71</t>
+          <t>1,0; 3,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,07</t>
+          <t>1,04; 3,0</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,73</t>
+          <t>0,64; 6,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,59</t>
+          <t>0,57; 5,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,98</t>
+          <t>0,94; 4,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,04</t>
+          <t>0,56; 5,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,53</t>
+          <t>0,38; 3,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,12</t>
+          <t>0,56; 4,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,81</t>
+          <t>1,55; 3,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,48</t>
+          <t>0,92; 4,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,39</t>
+          <t>0,7; 3,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,34</t>
+          <t>0,35; 3,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,44</t>
+          <t>1,43; 3,25</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,23</t>
+          <t>2,73; 4,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,04</t>
+          <t>2,71; 4,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,64</t>
+          <t>2,16; 3,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,2</t>
+          <t>2,35; 4,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,27</t>
+          <t>2,81; 4,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,36</t>
+          <t>2,94; 4,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,32</t>
+          <t>2,95; 4,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,7</t>
+          <t>3,07; 4,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,0; 4,01</t>
+          <t>2,97; 3,95</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,97</t>
+          <t>2,98; 3,96</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,72</t>
+          <t>2,76; 3,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,19</t>
+          <t>2,96; 4,15</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13372; 31583</t>
+          <t>13583; 30786</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24042; 46471</t>
+          <t>23835; 46987</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11694; 30152</t>
+          <t>11892; 30125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12954; 49668</t>
+          <t>13151; 56005</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19008; 37383</t>
+          <t>18465; 37534</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22783; 44808</t>
+          <t>22639; 44637</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18544; 37854</t>
+          <t>18369; 37300</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13126; 41944</t>
+          <t>12644; 38471</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36133; 60727</t>
+          <t>36390; 60708</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52228; 83612</t>
+          <t>52225; 82921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33727; 59339</t>
+          <t>34833; 60916</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30794; 74918</t>
+          <t>31603; 77433</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14767; 34249</t>
+          <t>14346; 34044</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17426; 39326</t>
+          <t>18214; 39873</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11282; 27559</t>
+          <t>11178; 28400</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12055; 34482</t>
+          <t>11722; 33835</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13483; 33069</t>
+          <t>13451; 33660</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20572; 45317</t>
+          <t>21723; 46626</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18519; 40016</t>
+          <t>18939; 39333</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19549; 51702</t>
+          <t>21148; 51712</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32474; 59669</t>
+          <t>32169; 61554</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43058; 76795</t>
+          <t>43090; 74339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33582; 59633</t>
+          <t>32853; 59956</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38384; 76356</t>
+          <t>38607; 73364</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5700; 17951</t>
+          <t>5630; 18280</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8839; 24962</t>
+          <t>8652; 25155</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11529; 29737</t>
+          <t>11278; 29373</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11414; 29338</t>
+          <t>10850; 28303</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10104; 26043</t>
+          <t>10058; 26416</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13763; 31912</t>
+          <t>13753; 31337</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8801; 24177</t>
+          <t>8211; 23147</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15237; 31112</t>
+          <t>15714; 31043</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17872; 39001</t>
+          <t>18899; 40054</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27579; 50818</t>
+          <t>26344; 51476</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23025; 45045</t>
+          <t>23202; 45859</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29189; 53211</t>
+          <t>30651; 52889</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8185; 24737</t>
+          <t>8514; 24285</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5030; 20730</t>
+          <t>4646; 19962</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3941; 16571</t>
+          <t>3937; 17072</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7401; 31319</t>
+          <t>7923; 31158</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4874; 17447</t>
+          <t>5171; 17242</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5528; 21045</t>
+          <t>6439; 22062</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9535; 27522</t>
+          <t>9344; 25847</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16217; 32445</t>
+          <t>15406; 31223</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16200; 35554</t>
+          <t>16151; 37946</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12971; 36280</t>
+          <t>14128; 35907</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16117; 36688</t>
+          <t>16350; 36644</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24416; 57921</t>
+          <t>24163; 56246</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>898; 8981</t>
+          <t>950; 8925</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1067; 14634</t>
+          <t>1054; 12164</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2150; 13680</t>
+          <t>2110; 12762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3434; 13691</t>
+          <t>3429; 13542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2968; 14617</t>
+          <t>2279; 13059</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1997; 11170</t>
+          <t>1940; 11143</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3278; 16288</t>
+          <t>3198; 14300</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9499; 21862</t>
+          <t>9955; 21229</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4886; 17613</t>
+          <t>5112; 18227</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4202; 18675</t>
+          <t>4224; 19819</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7912; 23189</t>
+          <t>7535; 21931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15520; 30368</t>
+          <t>15200; 29973</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4729; 16448</t>
+          <t>5280; 17173</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6557</t>
+          <t>0; 7081</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1018; 9120</t>
+          <t>905; 9355</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4802; 16318</t>
+          <t>4813; 15187</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3664; 15060</t>
+          <t>3754; 14660</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1888; 12251</t>
+          <t>1885; 13188</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2792; 15001</t>
+          <t>2168; 14452</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2490; 17585</t>
+          <t>2959; 17807</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10992; 26242</t>
+          <t>10430; 26322</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2839; 16073</t>
+          <t>2927; 15713</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4849; 18805</t>
+          <t>5055; 19493</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9049; 29455</t>
+          <t>9977; 28752</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>804; 7263</t>
+          <t>815; 7707</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1056; 10346</t>
+          <t>1047; 10637</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3927</t>
+          <t>0; 4467</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2145; 10959</t>
+          <t>2600; 11549</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1203; 10500</t>
+          <t>1171; 10814</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1153; 10667</t>
+          <t>1140; 11267</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1273; 11672</t>
+          <t>1280; 10536</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6112; 15571</t>
+          <t>6318; 15033</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3053; 15002</t>
+          <t>3070; 15025</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3538; 16497</t>
+          <t>3432; 16420</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1333; 12530</t>
+          <t>1328; 11756</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10004; 23531</t>
+          <t>9808; 22223</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>66285; 103953</t>
+          <t>66970; 104631</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>78057; 117722</t>
+          <t>78847; 118212</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>59575; 96885</t>
+          <t>57493; 93752</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>80315; 140899</t>
+          <t>78717; 138984</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>77527; 117081</t>
+          <t>77052; 115636</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>92956; 137195</t>
+          <t>92424; 134191</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>84044; 123999</t>
+          <t>84665; 123209</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>112051; 168116</t>
+          <t>109933; 165198</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156069; 208510</t>
+          <t>154068; 205090</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>183513; 240628</t>
+          <t>180317; 240083</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>153420; 205803</t>
+          <t>152832; 211060</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>202167; 290346</t>
+          <t>205341; 288038</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C07-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C07-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,57</t>
+          <t>3,45; 8,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 12,39</t>
+          <t>6,32; 12,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,54</t>
+          <t>3,33; 8,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 14,61</t>
+          <t>3,73; 12,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,98</t>
+          <t>4,88; 10,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,1; 12,03</t>
+          <t>6,2; 11,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 10,6</t>
+          <t>5,36; 11,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 12,67</t>
+          <t>4,14; 12,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,25</t>
+          <t>4,88; 8,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 11,05</t>
+          <t>7,08; 11,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,64</t>
+          <t>4,87; 8,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 11,27</t>
+          <t>4,93; 11,11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,91</t>
+          <t>2,51; 5,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,68</t>
+          <t>2,89; 6,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,76</t>
+          <t>2,36; 5,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,41</t>
+          <t>3,26; 9,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,15</t>
+          <t>2,42; 6,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,34</t>
+          <t>3,74; 8,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,92</t>
+          <t>3,6; 7,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,35</t>
+          <t>5,49; 10,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,48</t>
+          <t>2,91; 5,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,43</t>
+          <t>3,73; 6,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,06</t>
+          <t>3,37; 6,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 8,13</t>
+          <t>5,03; 8,92</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,63</t>
+          <t>0,96; 3,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,29</t>
+          <t>1,46; 4,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,27</t>
+          <t>2,12; 5,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,4</t>
+          <t>1,99; 5,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,38</t>
+          <t>1,71; 4,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,75</t>
+          <t>2,03; 4,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,04</t>
+          <t>1,46; 4,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,84</t>
+          <t>2,7; 5,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,62</t>
+          <t>1,65; 3,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,13</t>
+          <t>2,15; 4,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,05</t>
+          <t>2,04; 3,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,01</t>
+          <t>2,72; 4,77</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,0</t>
+          <t>2,02; 5,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,68</t>
+          <t>1,0; 3,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,33</t>
+          <t>0,79; 3,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,61</t>
+          <t>2,21; 5,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,93</t>
+          <t>1,17; 4,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,92</t>
+          <t>1,14; 3,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,74</t>
+          <t>1,71; 4,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,46</t>
+          <t>2,37; 4,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,5</t>
+          <t>1,89; 4,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,25</t>
+          <t>1,26; 3,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,47</t>
+          <t>1,55; 3,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,6</t>
+          <t>2,61; 4,36</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,28</t>
+          <t>0,39; 3,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,37</t>
+          <t>0,29; 3,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,44</t>
+          <t>0,55; 3,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,48</t>
+          <t>0,62; 2,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,09</t>
+          <t>0,92; 4,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,85</t>
+          <t>0,52; 2,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,61</t>
+          <t>0,81; 3,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,97</t>
+          <t>1,96; 4,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,08</t>
+          <t>0,86; 3,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,64</t>
+          <t>0,53; 2,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,86</t>
+          <t>0,94; 3,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,77</t>
+          <t>1,51; 2,91</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,07</t>
+          <t>2,25; 7,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,07</t>
+          <t>0,39; 3,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,23</t>
+          <t>1,26; 4,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,94</t>
+          <t>1,48; 5,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,39</t>
+          <t>0,63; 4,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,22</t>
+          <t>0,97; 4,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,97</t>
+          <t>1,58; 3,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,73</t>
+          <t>2,38; 5,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,79</t>
+          <t>0,52; 2,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,84</t>
+          <t>0,99; 3,73</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,0</t>
+          <t>1,75; 3,48</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,08</t>
+          <t>0,63; 5,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,75</t>
+          <t>0,57; 5,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,19</t>
+          <t>0,86; 4,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,19</t>
+          <t>0,54; 5,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,73</t>
+          <t>0,38; 3,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,62</t>
+          <t>0,57; 4,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,68</t>
+          <t>1,55; 3,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,49</t>
+          <t>0,93; 4,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,37</t>
+          <t>0,84; 3,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,14</t>
+          <t>0,35; 3,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,25</t>
+          <t>1,52; 3,37</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,26</t>
+          <t>2,74; 4,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,06</t>
+          <t>2,72; 4,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,52</t>
+          <t>2,26; 3,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,14</t>
+          <t>2,75; 4,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,22</t>
+          <t>2,85; 4,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,27</t>
+          <t>2,98; 4,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,3</t>
+          <t>2,87; 4,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,07; 4,62</t>
+          <t>3,52; 4,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,97; 3,95</t>
+          <t>2,94; 3,99</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,96</t>
+          <t>2,99; 3,95</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,82</t>
+          <t>2,78; 3,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,15</t>
+          <t>3,35; 4,39</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27138</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22776</t>
+          <t>25940</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50287</t>
+          <t>53079</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13583; 30786</t>
+          <t>12416; 29552</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23835; 46987</t>
+          <t>23969; 46713</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11892; 30125</t>
+          <t>11736; 28898</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13151; 56005</t>
+          <t>14133; 47248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18465; 37534</t>
+          <t>18358; 37715</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22639; 44637</t>
+          <t>22992; 43881</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18369; 37300</t>
+          <t>18852; 38786</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12644; 38471</t>
+          <t>14195; 43786</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36390; 60708</t>
+          <t>35917; 61106</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52225; 82921</t>
+          <t>53111; 84120</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34833; 60916</t>
+          <t>34301; 61846</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31603; 77433</t>
+          <t>35598; 80199</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>24292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36093</t>
+          <t>37840</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56299</t>
+          <t>62132</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14346; 34044</t>
+          <t>14457; 33992</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18214; 39873</t>
+          <t>17285; 39081</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11178; 28400</t>
+          <t>11630; 27580</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11722; 33835</t>
+          <t>14530; 40288</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13451; 33660</t>
+          <t>13269; 34271</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21723; 46626</t>
+          <t>20925; 45885</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18939; 39333</t>
+          <t>17874; 38383</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21148; 51712</t>
+          <t>26478; 51670</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32169; 61554</t>
+          <t>32742; 60193</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43090; 74339</t>
+          <t>43158; 77087</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32853; 59956</t>
+          <t>33360; 61769</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38607; 73364</t>
+          <t>46687; 82800</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>19843</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21982</t>
+          <t>23904</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40420</t>
+          <t>43747</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5630; 18280</t>
+          <t>4823; 18873</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8652; 25155</t>
+          <t>8572; 25363</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11278; 29373</t>
+          <t>11828; 30088</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10850; 28303</t>
+          <t>11957; 31523</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10058; 26416</t>
+          <t>10304; 27916</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13753; 31337</t>
+          <t>13366; 30354</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8211; 23147</t>
+          <t>8365; 23488</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15714; 31043</t>
+          <t>16420; 32697</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18899; 40054</t>
+          <t>18311; 39345</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26344; 51476</t>
+          <t>26827; 50982</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23202; 45859</t>
+          <t>23067; 45131</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30651; 52889</t>
+          <t>32862; 57589</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19471</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>24895</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42288</t>
+          <t>48090</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8514; 24285</t>
+          <t>8195; 23824</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4646; 19962</t>
+          <t>5455; 21629</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3937; 17072</t>
+          <t>4066; 17298</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7923; 31158</t>
+          <t>14974; 34870</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5171; 17242</t>
+          <t>5135; 17548</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6439; 22062</t>
+          <t>6402; 21173</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9344; 25847</t>
+          <t>9302; 26484</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15406; 31223</t>
+          <t>17101; 33289</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16151; 37946</t>
+          <t>15945; 36234</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14128; 35907</t>
+          <t>13887; 34978</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16350; 36644</t>
+          <t>16439; 38014</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24163; 56246</t>
+          <t>36542; 61032</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21813</t>
+          <t>25130</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>950; 8925</t>
+          <t>1063; 9707</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1054; 12164</t>
+          <t>1063; 12725</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2110; 12762</t>
+          <t>2059; 13491</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3429; 13542</t>
+          <t>3690; 15398</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2279; 13059</t>
+          <t>2933; 13453</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1940; 11143</t>
+          <t>2029; 11650</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3198; 14300</t>
+          <t>3213; 14689</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9955; 21229</t>
+          <t>11649; 24690</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5112; 18227</t>
+          <t>5058; 19436</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4224; 19819</t>
+          <t>4002; 18671</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7535; 21931</t>
+          <t>7227; 23499</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15200; 29973</t>
+          <t>17998; 34616</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>20298</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5280; 17173</t>
+          <t>4784; 16816</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7081</t>
+          <t>0; 6014</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>905; 9355</t>
+          <t>902; 9180</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4813; 15187</t>
+          <t>5031; 16267</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3754; 14660</t>
+          <t>3654; 14689</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1885; 13188</t>
+          <t>1885; 12867</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2168; 14452</t>
+          <t>2674; 13284</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2959; 17807</t>
+          <t>6795; 16500</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10430; 26322</t>
+          <t>10961; 27425</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2927; 15713</t>
+          <t>2901; 15924</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5055; 19493</t>
+          <t>5005; 18898</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9977; 28752</t>
+          <t>14429; 28757</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>11351</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15674</t>
+          <t>17450</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>815; 7707</t>
+          <t>802; 7364</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1047; 10637</t>
+          <t>1063; 10222</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4467</t>
+          <t>0; 4011</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2600; 11549</t>
+          <t>2596; 12613</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1171; 10814</t>
+          <t>1133; 11568</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1140; 11267</t>
+          <t>1153; 10153</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1280; 10536</t>
+          <t>1290; 10681</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6318; 15033</t>
+          <t>6904; 17381</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3070; 15025</t>
+          <t>3127; 14450</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3432; 16420</t>
+          <t>4102; 16192</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1328; 11756</t>
+          <t>1303; 12011</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9808; 22223</t>
+          <t>11387; 25242</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107520</t>
+          <t>117815</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>138358</t>
+          <t>152111</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>245878</t>
+          <t>269926</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>66970; 104631</t>
+          <t>67347; 103332</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>78847; 118212</t>
+          <t>79376; 119741</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>57493; 93752</t>
+          <t>60136; 94876</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>78717; 138984</t>
+          <t>93329; 147596</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>77052; 115636</t>
+          <t>78134; 115038</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>92424; 134191</t>
+          <t>93902; 138327</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>84665; 123209</t>
+          <t>82376; 121465</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>109933; 165198</t>
+          <t>127565; 176936</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154068; 205090</t>
+          <t>152983; 207455</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>180317; 240083</t>
+          <t>181344; 239580</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>152832; 211060</t>
+          <t>153503; 208873</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>205341; 288038</t>
+          <t>235502; 308107</t>
         </is>
       </c>
     </row>
